--- a/artfynd/A 18280-2021 artfynd.xlsx
+++ b/artfynd/A 18280-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18280-2021 artfynd.xlsx
+++ b/artfynd/A 18280-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,130 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123402184</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57848</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skogshyddan, Erstavik, Erstavik, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>683065</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6573936</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mathias Bergström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mathias Bergström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18280-2021 artfynd.xlsx
+++ b/artfynd/A 18280-2021 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>123402184</v>
       </c>
       <c r="B3" t="n">
-        <v>57848</v>
+        <v>57851</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 18280-2021 artfynd.xlsx
+++ b/artfynd/A 18280-2021 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>123402184</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
+        <v>57857</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 18280-2021 artfynd.xlsx
+++ b/artfynd/A 18280-2021 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>123402184</v>
       </c>
       <c r="B3" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 18280-2021 artfynd.xlsx
+++ b/artfynd/A 18280-2021 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>123402184</v>
       </c>
       <c r="B3" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 18280-2021 artfynd.xlsx
+++ b/artfynd/A 18280-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -921,6 +921,293 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130814860</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Erstavik, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>683038</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6573948</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130814861</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91270</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5734</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Druvfingersvampar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Erstavik, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>683018</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6573930</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130814862</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Erstavik, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>683020</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6573927</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18280-2021 artfynd.xlsx
+++ b/artfynd/A 18280-2021 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>130814861</v>
       </c>
       <c r="B5" t="n">
-        <v>91270</v>
+        <v>91271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
